--- a/ABA_mining/outputs/eval/task3/price/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/zero_shot/Contrary(P)Body(N).xlsx
@@ -30681,16 +30681,16 @@
         <v>44</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M2" t="n">
         <v>0.89</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O2" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="3">
@@ -30740,16 +30740,16 @@
         <v>44</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M3" t="n">
         <v>0.89</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O3" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="4">
@@ -30799,16 +30799,16 @@
         <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8942065491183879</v>
+        <v>0.894207</v>
       </c>
       <c r="M4" t="n">
         <v>0.8875</v>
       </c>
       <c r="N4" t="n">
-        <v>0.890840652446675</v>
+        <v>0.890841</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8087912087912088</v>
+        <v>0.808791</v>
       </c>
     </row>
   </sheetData>
